--- a/testbuild/ValueSet-no-basis-family-relation.valueset.xlsx
+++ b/testbuild/ValueSet-no-basis-family-relation.valueset.xlsx
@@ -30,13 +30,13 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.3-test</t>
+    <t>2.2.4-test</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>NoBasisFamilyRelationVS</t>
+    <t>NoBasisFamilyRelation</t>
   </si>
   <si>
     <t>Title</t>
